--- a/SourceData/Datas/__tables__.xlsx
+++ b/SourceData/Datas/__tables__.xlsx
@@ -1930,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="1"/>
@@ -2098,184 +2098,320 @@
       </c>
     </row>
     <row r="4" ht="13.5" customHeight="1" s="1">
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="0" t="inlineStr">
         <is>
           <t>TCondition</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="0" t="inlineStr">
         <is>
           <t>CCondition</t>
         </is>
       </c>
-      <c r="D4" t="b">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E4" s="0" t="inlineStr">
         <is>
           <t>condition.xlsx</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="G4" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" s="0" t="inlineStr">
         <is>
           <t>条件模板</t>
         </is>
       </c>
     </row>
     <row r="5" ht="13.5" customHeight="1" s="1">
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="0" t="inlineStr">
         <is>
           <t>TCraftRecipe</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="0" t="inlineStr">
         <is>
           <t>CCraftRecipe</t>
         </is>
       </c>
-      <c r="D5" t="b">
+      <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E5" s="0" t="inlineStr">
         <is>
           <t>craft_recipe.xlsx</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G5" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H5" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" s="0" t="inlineStr">
         <is>
           <t>合成配方</t>
         </is>
       </c>
     </row>
     <row r="6" ht="13.5" customHeight="1" s="1">
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="0" t="inlineStr">
         <is>
           <t>TCraftCost</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="0" t="inlineStr">
         <is>
           <t>CCraftCost</t>
         </is>
       </c>
-      <c r="D6" t="b">
+      <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E6" s="0" t="inlineStr">
         <is>
           <t>craft_cost.xlsx</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="G6" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H6" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" s="0" t="inlineStr">
         <is>
           <t>合成消耗</t>
         </is>
       </c>
     </row>
     <row r="7" ht="13.5" customHeight="1" s="1">
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="0" t="inlineStr">
         <is>
           <t>TQuest</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="0" t="inlineStr">
         <is>
           <t>CQuest</t>
         </is>
       </c>
-      <c r="D7" t="b">
+      <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E7" s="0" t="inlineStr">
         <is>
           <t>quest.xlsx</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G7" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H7" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" s="0" t="inlineStr">
         <is>
           <t>主线任务</t>
         </is>
       </c>
     </row>
     <row r="8" ht="13.5" customHeight="1" s="1">
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="0" t="inlineStr">
         <is>
           <t>TGoto</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>CGoto</t>
         </is>
       </c>
-      <c r="D8" t="b">
+      <c r="D8" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E8" s="0" t="inlineStr">
         <is>
           <t>goto.xlsx</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G8" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" s="0" t="inlineStr">
         <is>
           <t>引导跳转</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="13.5" customHeight="1" s="1"/>
-    <row r="10" ht="13.5" customHeight="1" s="1"/>
-    <row r="11" ht="14.5" customHeight="1" s="1"/>
-    <row r="12" ht="14.5" customHeight="1" s="1"/>
+    <row r="9" ht="13.5" customHeight="1" s="1">
+      <c r="B9" s="0" t="inlineStr">
+        <is>
+          <t>TFlag</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>CFlag</t>
+        </is>
+      </c>
+      <c r="D9" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="0" t="inlineStr">
+        <is>
+          <t>flag.xlsx</t>
+        </is>
+      </c>
+      <c r="G9" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I9" s="0" t="inlineStr">
+        <is>
+          <t>剧情旗标</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="13.5" customHeight="1" s="1">
+      <c r="B10" s="0" t="inlineStr">
+        <is>
+          <t>TItem</t>
+        </is>
+      </c>
+      <c r="C10" s="0" t="inlineStr">
+        <is>
+          <t>CItem</t>
+        </is>
+      </c>
+      <c r="D10" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="0" t="inlineStr">
+        <is>
+          <t>item.xlsx</t>
+        </is>
+      </c>
+      <c r="G10" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I10" s="0" t="inlineStr">
+        <is>
+          <t>物品显示名</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="14.5" customHeight="1" s="1">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>TDialogue</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CDialogue</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>dialogue.xlsx</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>对白脚本目录</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="14.5" customHeight="1" s="1">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>TChat</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CChat</t>
+        </is>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>chat.xlsx</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>对白台词行</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="14.5" customHeight="1" s="1"/>
     <row r="14" ht="14.5" customHeight="1" s="1"/>
     <row r="15" ht="14.5" customHeight="1" s="1"/>

--- a/SourceData/Datas/__tables__.xlsx
+++ b/SourceData/Datas/__tables__.xlsx
@@ -1930,7 +1930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K12"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="9" customWidth="1" style="1" min="1" max="1"/>
@@ -2338,82 +2338,150 @@
       </c>
       <c r="I10" s="0" t="inlineStr">
         <is>
-          <t>物品显示名</t>
+          <t>基础物品表</t>
         </is>
       </c>
     </row>
     <row r="11" ht="14.5" customHeight="1" s="1">
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="0" t="inlineStr">
         <is>
           <t>TDialogue</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="0" t="inlineStr">
         <is>
           <t>CDialogue</t>
         </is>
       </c>
-      <c r="D11" t="b">
+      <c r="D11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E11" s="0" t="inlineStr">
         <is>
           <t>dialogue.xlsx</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="G11" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H11" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I11" s="0" t="inlineStr">
         <is>
           <t>对白脚本目录</t>
         </is>
       </c>
     </row>
     <row r="12" ht="14.5" customHeight="1" s="1">
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="0" t="inlineStr">
         <is>
           <t>TChat</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="0" t="inlineStr">
         <is>
           <t>CChat</t>
         </is>
       </c>
-      <c r="D12" t="b">
+      <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E12" s="0" t="inlineStr">
         <is>
           <t>chat.xlsx</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G12" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H12" s="0" t="inlineStr">
         <is>
           <t>c</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I12" s="0" t="inlineStr">
         <is>
           <t>对白台词行</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="14.5" customHeight="1" s="1"/>
-    <row r="14" ht="14.5" customHeight="1" s="1"/>
+    <row r="13" ht="14.5" customHeight="1" s="1">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>TDisplay</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CDisplay</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>display.xlsx</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>展示配置表</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="14.5" customHeight="1" s="1">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>TDisplayTemplate</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CDisplayTemplate</t>
+        </is>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>display_template.xlsx</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>c</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>展示模板表</t>
+        </is>
+      </c>
+    </row>
     <row r="15" ht="14.5" customHeight="1" s="1"/>
     <row r="16" ht="14.5" customHeight="1" s="1"/>
     <row r="17" ht="14.5" customHeight="1" s="1"/>
